--- a/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513657_FASEFINALAFFA2_PROCESSED.xlsx
+++ b/informes_data/Tercera FEB/2025-26/playoffs/individual/NP_play_by_play_2513657_FASEFINALAFFA2_PROCESSED.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.865</v>
+        <v>6.7113</v>
       </c>
       <c r="E2" t="n">
-        <v>8.1075</v>
+        <v>7.8704</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2425</v>
+        <v>-1.159</v>
       </c>
       <c r="G2" t="n">
         <v>4.1064</v>
@@ -610,13 +610,13 @@
         <v>1.5579</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2965</v>
+        <v>0.1428</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2437</v>
+        <v>0.0065</v>
       </c>
       <c r="U2" t="n">
-        <v>0.0529</v>
+        <v>0.1363</v>
       </c>
       <c r="V2" t="n">
         <v>1.0989</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>H. GOMEZ GARCIA</t>
+          <t>J. RODENAS SANCHEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.5764</v>
+        <v>1.7327</v>
       </c>
       <c r="E3" t="n">
-        <v>3.27</v>
+        <v>1.1291</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6936</v>
+        <v>0.6036</v>
       </c>
       <c r="G3" t="n">
-        <v>1.0555</v>
+        <v>0.4547</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.9274</v>
+        <v>0.0703</v>
       </c>
       <c r="I3" t="n">
-        <v>2.9829</v>
+        <v>0.3844</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3922</v>
+        <v>1.7493</v>
       </c>
       <c r="K3" t="n">
-        <v>-1.288</v>
+        <v>1.0597</v>
       </c>
       <c r="L3" t="n">
-        <v>3.6802</v>
+        <v>0.6896</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.3367</v>
+        <v>-1.2946</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6394</v>
+        <v>-0.9893999999999999</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.6973</v>
+        <v>-0.3052</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.3632</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.5579</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.578</v>
+        <v>-0.0851</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.3433</v>
+        <v>-0.4254</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.2347</v>
+        <v>0.3403</v>
       </c>
       <c r="V3" t="n">
-        <v>1.0989</v>
+        <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2211</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.1221</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. RODENAS SANCHEZ</t>
+          <t>H. GOMEZ GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0541</v>
+        <v>1.6544</v>
       </c>
       <c r="E4" t="n">
-        <v>0.8679</v>
+        <v>3.4315</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1862</v>
+        <v>-1.777</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4547</v>
+        <v>1.0555</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0703</v>
+        <v>-1.9274</v>
       </c>
       <c r="I4" t="n">
-        <v>0.3844</v>
+        <v>2.9829</v>
       </c>
       <c r="J4" t="n">
-        <v>1.7493</v>
+        <v>2.3922</v>
       </c>
       <c r="K4" t="n">
-        <v>1.0597</v>
+        <v>-1.288</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6896</v>
+        <v>3.6802</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2946</v>
+        <v>-1.3367</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.9893999999999999</v>
+        <v>-0.6394</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3052</v>
+        <v>-0.6973</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3632</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.1947</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.5579</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.7637</v>
+        <v>-0.5</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6866</v>
+        <v>-0.1818</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0771</v>
+        <v>-0.3182</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.0989</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.2211</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. GADEA HIERRO</t>
+          <t>A. MONRABAL ROMEU</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0307</v>
+        <v>0.5685</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.6403</v>
+        <v>1.8729</v>
       </c>
       <c r="F5" t="n">
-        <v>1.671</v>
+        <v>-1.3044</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3758</v>
+        <v>1.6343</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.4522</v>
+        <v>-0.1565</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0763</v>
+        <v>1.7909</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5983000000000001</v>
+        <v>3.5526</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2956</v>
+        <v>0.7723</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6973</v>
+        <v>2.7802</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2225</v>
+        <v>-1.9182</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.1565</v>
+        <v>-0.9288999999999999</v>
       </c>
       <c r="O5" t="n">
-        <v>0.379</v>
+        <v>-0.9893</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.1947</v>
+        <v>0.3895</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9737</v>
+        <v>-1.1684</v>
       </c>
       <c r="R5" t="n">
-        <v>0.7789</v>
+        <v>1.5579</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7234</v>
+        <v>-0.1121</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.0683</v>
+        <v>-0.5113</v>
       </c>
       <c r="U5" t="n">
-        <v>0.7917</v>
+        <v>0.3991</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1221</v>
+        <v>-1.3432</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1221</v>
+        <v>-1.3432</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. MASIP CANTERO</t>
+          <t>A. GADEA HIERRO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.2316</v>
+        <v>-0.3032</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3359</v>
+        <v>-1.6403</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.5675</v>
+        <v>1.3371</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.4668</v>
+        <v>-0.3758</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7195</v>
+        <v>-1.4522</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2527</v>
+        <v>1.0763</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1384</v>
+        <v>-0.5983000000000001</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0077</v>
+        <v>-1.2956</v>
       </c>
       <c r="L6" t="n">
-        <v>0.146</v>
+        <v>0.6973</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6051</v>
+        <v>0.2225</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7118</v>
+        <v>-0.1565</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1067</v>
+        <v>0.379</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.1947</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0959</v>
+        <v>0.3895</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1975</v>
+        <v>-0.0683</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2934</v>
+        <v>0.4578</v>
       </c>
       <c r="V6" t="n">
-        <v>0.3311</v>
+        <v>-0.1221</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3311</v>
+        <v>-0.1221</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. MONRABAL ROMEU</t>
+          <t>D. MASIP CANTERO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.2467</v>
+        <v>-0.6025</v>
       </c>
       <c r="E7" t="n">
-        <v>1.1133</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.36</v>
+        <v>-0.5397</v>
       </c>
       <c r="G7" t="n">
-        <v>1.6343</v>
+        <v>-0.4668</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1565</v>
+        <v>-0.7195</v>
       </c>
       <c r="I7" t="n">
-        <v>1.7909</v>
+        <v>0.2527</v>
       </c>
       <c r="J7" t="n">
-        <v>3.5526</v>
+        <v>0.1384</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7723</v>
+        <v>-0.0077</v>
       </c>
       <c r="L7" t="n">
-        <v>2.7802</v>
+        <v>0.146</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.9182</v>
+        <v>-0.6051</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.9288999999999999</v>
+        <v>-0.7118</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9893</v>
+        <v>0.1067</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3895</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1684</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.5579</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.9273</v>
+        <v>-0.4668</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.2708</v>
+        <v>-0.2012</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3435</v>
+        <v>-0.2656</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.3432</v>
+        <v>0.3311</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.3432</v>
+        <v>0.3311</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.1823</v>
+        <v>-1.8901</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.9322</v>
+        <v>-1.6678</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2502</v>
+        <v>-0.2223</v>
       </c>
       <c r="G8" t="n">
         <v>-3.3863</v>
@@ -1078,13 +1078,13 @@
         <v>1.5579</v>
       </c>
       <c r="S8" t="n">
-        <v>1.2424</v>
+        <v>0.5346</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8279</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4145</v>
+        <v>0.4423</v>
       </c>
       <c r="V8" t="n">
         <v>-0.4016</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.5358</v>
+        <v>-3.4037</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0665</v>
+        <v>-1.7675</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.4693</v>
+        <v>-1.6362</v>
       </c>
       <c r="G9" t="n">
         <v>-1.5297</v>
@@ -1156,13 +1156,13 @@
         <v>0.7789</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6429</v>
+        <v>-0.5108</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.838</v>
+        <v>-0.539</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1951</v>
+        <v>0.0281</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-5.1344</v>
+        <v>-5.0626</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.7277</v>
+        <v>-3.628</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4067</v>
+        <v>-1.4345</v>
       </c>
       <c r="G10" t="n">
         <v>-2.2132</v>
@@ -1234,13 +1234,13 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.4791</v>
+        <v>-0.4072</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5473</v>
+        <v>-0.4476</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0682</v>
+        <v>0.0404</v>
       </c>
       <c r="V10" t="n">
         <v>-2.4421</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.7359</v>
+        <v>-6.6362</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.7845</v>
+        <v>-4.6849</v>
       </c>
       <c r="F11" t="n">
         <v>-1.9513</v>
@@ -1312,10 +1312,10 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5842000000000001</v>
+        <v>-0.4845</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3618</v>
+        <v>-0.2621</v>
       </c>
       <c r="U11" t="n">
         <v>-0.2224</v>
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.540500000000001</v>
+        <v>-7.231400000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5433999999999992</v>
+        <v>0.852599999999998</v>
       </c>
       <c r="F12" t="n">
-        <v>-8.0839</v>
+        <v>-8.0837</v>
       </c>
       <c r="G12" t="n">
-        <v>-3.7041</v>
+        <v>-3.704100000000001</v>
       </c>
       <c r="H12" t="n">
         <v>-9.783099999999999</v>
@@ -1378,7 +1378,7 @@
         <v>-7.1179</v>
       </c>
       <c r="O12" t="n">
-        <v>-5.012300000000001</v>
+        <v>-5.012299999999999</v>
       </c>
       <c r="P12" t="n">
         <v>0.9737999999999998</v>
@@ -1390,13 +1390,13 @@
         <v>7.789400000000001</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.8088</v>
+        <v>-1.4996</v>
       </c>
       <c r="T12" t="n">
-        <v>-2.847</v>
+        <v>-2.5379</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0383</v>
+        <v>1.0381</v>
       </c>
       <c r="V12" t="n">
         <v>-3.0012</v>
@@ -1405,7 +1405,7 @@
         <v>1.7801</v>
       </c>
       <c r="X12" t="n">
-        <v>-4.781099999999999</v>
+        <v>-4.7811</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>5.049</v>
+        <v>6.1338</v>
       </c>
       <c r="E13" t="n">
-        <v>5.5989</v>
+        <v>6.3963</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.5499000000000001</v>
+        <v>-0.2625</v>
       </c>
       <c r="G13" t="n">
         <v>1.9424</v>
@@ -1468,13 +1468,13 @@
         <v>0.9737</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2533</v>
+        <v>0.8315</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6802</v>
+        <v>0.1172</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4269</v>
+        <v>0.7143</v>
       </c>
       <c r="V13" t="n">
         <v>2.3862</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. LLOVET CAMP</t>
+          <t>Q. SALVANS HIDALGO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.0983</v>
+        <v>2.3687</v>
       </c>
       <c r="E14" t="n">
-        <v>1.4835</v>
+        <v>1.6395</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6148</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1.2203</v>
+        <v>2.0106</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9403</v>
+        <v>2.1727</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.72</v>
+        <v>-0.1621</v>
       </c>
       <c r="J14" t="n">
-        <v>1.8084</v>
+        <v>2.6723</v>
       </c>
       <c r="K14" t="n">
-        <v>1.5652</v>
+        <v>1.3266</v>
       </c>
       <c r="L14" t="n">
-        <v>0.2432</v>
+        <v>1.3457</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.5881</v>
+        <v>-0.6617</v>
       </c>
       <c r="N14" t="n">
-        <v>0.3751</v>
+        <v>0.8461</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9631</v>
+        <v>-1.5078</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7789</v>
+        <v>0.7789</v>
       </c>
       <c r="Q14" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R14" t="n">
-        <v>0.1947</v>
+        <v>0.7789</v>
       </c>
       <c r="S14" t="n">
-        <v>1.6569</v>
+        <v>0.6283</v>
       </c>
       <c r="T14" t="n">
-        <v>0.6488</v>
+        <v>-0.0397</v>
       </c>
       <c r="U14" t="n">
-        <v>1.0081</v>
+        <v>0.6679</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>-1.049</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>-0.9932</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.0559</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Q. SALVANS HIDALGO</t>
+          <t>S. COSTA I VÁZQUEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.9198</v>
+        <v>1.8237</v>
       </c>
       <c r="E15" t="n">
-        <v>1.5398</v>
+        <v>1.8237</v>
       </c>
       <c r="F15" t="n">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>2.0106</v>
+        <v>1.8237</v>
       </c>
       <c r="H15" t="n">
-        <v>2.1727</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.1621</v>
+        <v>1.8237</v>
       </c>
       <c r="J15" t="n">
-        <v>2.6723</v>
+        <v>1.8237</v>
       </c>
       <c r="K15" t="n">
-        <v>1.3266</v>
+        <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3457</v>
+        <v>1.8237</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.6617</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8461</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.5078</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1793</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1393</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3187</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.049</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.9932</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.0559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>S. COSTA I VÁZQUEZ</t>
+          <t>J. NOGUES JARNE</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.8237</v>
+        <v>1.5881</v>
       </c>
       <c r="E16" t="n">
-        <v>1.8237</v>
+        <v>2.2478</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="G16" t="n">
-        <v>1.8237</v>
+        <v>1.4126</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="I16" t="n">
-        <v>1.8237</v>
+        <v>0.2026</v>
       </c>
       <c r="J16" t="n">
-        <v>1.8237</v>
+        <v>3.1191</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>1.6678</v>
       </c>
       <c r="L16" t="n">
-        <v>1.8237</v>
+        <v>1.4512</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-1.7064</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-0.4578</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-1.2486</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>-0.3895</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>0.5842000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>0.9003</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.1025</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.7978</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>-0.3354</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-0.3354</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>J. NOGUES JARNE</t>
+          <t>I. LLOVET CAMP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.6554</v>
+        <v>1.3927</v>
       </c>
       <c r="E17" t="n">
-        <v>2.5469</v>
+        <v>0.9851</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.8915</v>
+        <v>0.4075</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4126</v>
+        <v>1.2203</v>
       </c>
       <c r="H17" t="n">
-        <v>1.21</v>
+        <v>1.9403</v>
       </c>
       <c r="I17" t="n">
-        <v>0.2026</v>
+        <v>-0.72</v>
       </c>
       <c r="J17" t="n">
-        <v>3.1191</v>
+        <v>1.8084</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6678</v>
+        <v>1.5652</v>
       </c>
       <c r="L17" t="n">
-        <v>1.4512</v>
+        <v>0.2432</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.7064</v>
+        <v>-0.5881</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.4578</v>
+        <v>0.3751</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.2486</v>
+        <v>-0.9631</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3895</v>
+        <v>-0.7789</v>
       </c>
       <c r="Q17" t="n">
         <v>-0.9737</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5842000000000001</v>
+        <v>0.1947</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9676</v>
+        <v>0.9513</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4015</v>
+        <v>0.1504</v>
       </c>
       <c r="U17" t="n">
-        <v>0.5661</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3354</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3354</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. SESE FRASNEDO</t>
+          <t>T. SMALLWOOD</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5238</v>
+        <v>1.0093</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0388</v>
+        <v>2.304</v>
       </c>
       <c r="F18" t="n">
-        <v>0.485</v>
+        <v>-1.2947</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.9585</v>
+        <v>0.8017</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.07240000000000001</v>
+        <v>1.8119</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.8862</v>
+        <v>-1.0102</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.0614</v>
+        <v>2.1581</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1078</v>
+        <v>2.0526</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.1692</v>
+        <v>0.1055</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.8972</v>
+        <v>-1.3564</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1802</v>
+        <v>-0.2407</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.717</v>
+        <v>-1.1157</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7789</v>
+        <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.9737</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7789</v>
+        <v>0.9737</v>
       </c>
       <c r="S18" t="n">
-        <v>0.09279999999999999</v>
+        <v>0.2635</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5104</v>
+        <v>-0.1015</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6032</v>
+        <v>0.365</v>
       </c>
       <c r="V18" t="n">
-        <v>0.6105</v>
+        <v>-0.0559</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6105</v>
+        <v>1.2211</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.277</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>T. SMALLWOOD</t>
+          <t>M. SESE FRASNEDO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.143</v>
+        <v>0.6783</v>
       </c>
       <c r="E19" t="n">
-        <v>2.2043</v>
+        <v>0.0388</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.0614</v>
+        <v>0.6395</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8017</v>
+        <v>-0.9585</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8119</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.0102</v>
+        <v>-0.8862</v>
       </c>
       <c r="J19" t="n">
-        <v>2.1581</v>
+        <v>-0.0614</v>
       </c>
       <c r="K19" t="n">
-        <v>2.0526</v>
+        <v>0.1078</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1055</v>
+        <v>-0.1692</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.3564</v>
+        <v>-0.8972</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2407</v>
+        <v>-0.1802</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1157</v>
+        <v>-0.717</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>0.7789</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.9737</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9737</v>
+        <v>0.7789</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.6028</v>
+        <v>0.2473</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2012</v>
+        <v>-0.5104</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4017</v>
+        <v>0.7577</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.0559</v>
+        <v>0.6105</v>
       </c>
       <c r="W19" t="n">
-        <v>1.2211</v>
+        <v>0.6105</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.277</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RUIZ CANAMERO</t>
+          <t>S. COSTA I VAZQUEZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.5038</v>
+        <v>-0.3571</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.7476</v>
+        <v>-1.4847</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2438</v>
+        <v>1.1276</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.3647</v>
+        <v>-1.8576</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.2658</v>
+        <v>0.4572</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0989</v>
+        <v>-2.3148</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.624</v>
+        <v>-2.3328</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.6645</v>
+        <v>-0.5824</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0405</v>
+        <v>-1.7504</v>
       </c>
       <c r="M20" t="n">
-        <v>0.2592</v>
+        <v>0.4752</v>
       </c>
       <c r="N20" t="n">
-        <v>0.3987</v>
+        <v>1.0396</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.1395</v>
+        <v>-0.5644</v>
       </c>
       <c r="P20" t="n">
-        <v>0.1947</v>
+        <v>0.3895</v>
       </c>
       <c r="Q20" t="n">
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.1947</v>
+        <v>0.3895</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.3338</v>
+        <v>-0.3895</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1237</v>
+        <v>-0.6525</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2102</v>
+        <v>0.263</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.5005</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. MARTINEZ PINO</t>
+          <t>A. RUIZ CANAMERO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,58 +2047,58 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0075</v>
+        <v>-0.4203</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.287</v>
+        <v>-0.7476</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2796</v>
+        <v>0.3273</v>
       </c>
       <c r="G21" t="n">
-        <v>0.4235</v>
+        <v>-0.3647</v>
       </c>
       <c r="H21" t="n">
-        <v>2.0172</v>
+        <v>-0.2658</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.5936</v>
+        <v>-0.0989</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4023</v>
+        <v>-0.624</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0263</v>
+        <v>-0.6645</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.624</v>
+        <v>0.0405</v>
       </c>
       <c r="M21" t="n">
-        <v>0.0212</v>
+        <v>0.2592</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9908</v>
+        <v>0.3987</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9697</v>
+        <v>-0.1395</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.1684</v>
+        <v>0.1947</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9474</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.7789</v>
+        <v>0.1947</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2626</v>
+        <v>-0.2503</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.742</v>
+        <v>-0.1237</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4794</v>
+        <v>-0.1267</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. CODINACHS PITA</t>
+          <t>I. MARTINEZ PINO</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.2891</v>
+        <v>-0.615</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.9779</v>
+        <v>-1.8883</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6887</v>
+        <v>1.2733</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3621</v>
+        <v>0.4235</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2637</v>
+        <v>2.0172</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.6258</v>
+        <v>-1.5936</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5417</v>
+        <v>0.4023</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.2206</v>
+        <v>1.0263</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7623</v>
+        <v>-0.624</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.9036999999999999</v>
+        <v>0.0212</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4843</v>
+        <v>0.9908</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.3881</v>
+        <v>-0.9697</v>
       </c>
       <c r="P22" t="n">
+        <v>-1.1684</v>
+      </c>
+      <c r="Q22" t="n">
         <v>-1.9474</v>
       </c>
-      <c r="Q22" t="n">
-        <v>-2.921</v>
-      </c>
       <c r="R22" t="n">
-        <v>0.9737</v>
+        <v>0.7789</v>
       </c>
       <c r="S22" t="n">
-        <v>1.0203</v>
+        <v>0.1299</v>
       </c>
       <c r="T22" t="n">
-        <v>0.4015</v>
+        <v>-0.3433</v>
       </c>
       <c r="U22" t="n">
-        <v>0.6188</v>
+        <v>0.4732</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2191,7 +2191,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. OMOARUNA OSAZUWA</t>
+          <t>A. CODINACHS PITA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4268</v>
+        <v>-1.5736</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.256</v>
+        <v>-2.3766</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1707</v>
+        <v>0.8028999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.3877</v>
+        <v>-0.3621</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.0097</v>
+        <v>0.2637</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.3779</v>
+        <v>-0.6258</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.214</v>
+        <v>0.5417</v>
       </c>
       <c r="K23" t="n">
-        <v>0.07439999999999999</v>
+        <v>-0.2206</v>
       </c>
       <c r="L23" t="n">
-        <v>-1.2885</v>
+        <v>0.7623</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.1736</v>
+        <v>-0.9036999999999999</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.0842</v>
+        <v>0.4843</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.0895</v>
+        <v>-1.3881</v>
       </c>
       <c r="P23" t="n">
-        <v>0.1947</v>
+        <v>-1.9474</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-2.921</v>
       </c>
       <c r="R23" t="n">
-        <v>0.1947</v>
+        <v>0.9737</v>
       </c>
       <c r="S23" t="n">
-        <v>0.8221000000000001</v>
+        <v>0.7358</v>
       </c>
       <c r="T23" t="n">
-        <v>0.958</v>
+        <v>0.0028</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1359</v>
+        <v>0.733</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.0559</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-0.0559</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>S. COSTA I VAZQUEZ</t>
+          <t>J. OMOARUNA OSAZUWA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.4452</v>
+        <v>-1.8301</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.8834</v>
+        <v>-0.8541</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4382</v>
+        <v>-0.976</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.8576</v>
+        <v>-2.3877</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4572</v>
+        <v>-0.0097</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3148</v>
+        <v>-2.3779</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.3328</v>
+        <v>-1.214</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.5824</v>
+        <v>0.07439999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.7504</v>
+        <v>-1.2885</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4752</v>
+        <v>-1.1736</v>
       </c>
       <c r="N24" t="n">
-        <v>1.0396</v>
+        <v>-0.0842</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.5644</v>
+        <v>-1.0895</v>
       </c>
       <c r="P24" t="n">
-        <v>0.3895</v>
+        <v>0.1947</v>
       </c>
       <c r="Q24" t="n">
         <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>0.3895</v>
+        <v>0.1947</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.4776</v>
+        <v>0.4188</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0512</v>
+        <v>0.3599</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.4264</v>
+        <v>0.0588</v>
       </c>
       <c r="V24" t="n">
-        <v>1.5005</v>
+        <v>-0.0559</v>
       </c>
       <c r="W24" t="n">
-        <v>1.5005</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>-0.0559</v>
       </c>
     </row>
     <row r="25">
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.540600000000001</v>
+        <v>10.1985</v>
       </c>
       <c r="E25" t="n">
-        <v>8.084000000000003</v>
+        <v>8.083899999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.5433999999999999</v>
+        <v>2.1145</v>
       </c>
       <c r="G25" t="n">
         <v>3.7042</v>
@@ -2374,7 +2374,7 @@
         <v>9.783199999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-6.079</v>
+        <v>-6.079000000000001</v>
       </c>
       <c r="J25" t="n">
         <v>12.1304</v>
@@ -2395,7 +2395,7 @@
         <v>-11.0915</v>
       </c>
       <c r="P25" t="n">
-        <v>-0.9738</v>
+        <v>-0.9737999999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-7.7895</v>
@@ -2404,13 +2404,13 @@
         <v>6.815600000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>1.8089</v>
+        <v>4.4669</v>
       </c>
       <c r="T25" t="n">
-        <v>-1.0382</v>
+        <v>-1.0383</v>
       </c>
       <c r="U25" t="n">
-        <v>2.847</v>
+        <v>5.5049</v>
       </c>
       <c r="V25" t="n">
         <v>3.001</v>
